--- a/data.xlsx
+++ b/data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="339">
   <si>
     <t>No</t>
   </si>
@@ -943,9 +943,6 @@
   </si>
   <si>
     <t>AHMAD ALFAN</t>
-  </si>
-  <si>
-    <t>5B</t>
   </si>
   <si>
     <t>12602</t>
@@ -8644,8 +8641,8 @@
       <c r="K58" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L58" s="7" t="s">
-        <v>310</v>
+      <c r="L58" s="15">
+        <v>5.0</v>
       </c>
       <c r="M58" s="12" t="s">
         <v>185</v>
@@ -8739,16 +8736,16 @@
     </row>
     <row r="59">
       <c r="A59" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="21"/>
       <c r="D59" s="22"/>
       <c r="E59" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="F59" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="G59" s="9">
         <v>41855.0</v>
@@ -8765,11 +8762,11 @@
       <c r="K59" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L59" s="7" t="s">
-        <v>310</v>
+      <c r="L59" s="15">
+        <v>5.0</v>
       </c>
       <c r="M59" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N59" s="7" t="s">
         <v>52</v>
@@ -8860,19 +8857,19 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="21"/>
       <c r="D60" s="22"/>
       <c r="E60" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="F60" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="G60" s="13" t="s">
         <v>317</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>318</v>
       </c>
       <c r="H60" s="20" t="s">
         <v>63</v>
@@ -8886,8 +8883,8 @@
       <c r="K60" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L60" s="7" t="s">
-        <v>310</v>
+      <c r="L60" s="15">
+        <v>5.0</v>
       </c>
       <c r="M60" s="12" t="s">
         <v>185</v>
@@ -8981,16 +8978,16 @@
     </row>
     <row r="61">
       <c r="A61" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="21"/>
       <c r="D61" s="22"/>
       <c r="E61" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="F61" s="12" t="s">
         <v>320</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>321</v>
       </c>
       <c r="G61" s="9">
         <v>41586.0</v>
@@ -9007,11 +9004,11 @@
       <c r="K61" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L61" s="7" t="s">
-        <v>310</v>
+      <c r="L61" s="15">
+        <v>5.0</v>
       </c>
       <c r="M61" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>52</v>
@@ -9102,19 +9099,19 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="21"/>
       <c r="D62" s="22"/>
       <c r="E62" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="G62" s="13" t="s">
         <v>325</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>326</v>
       </c>
       <c r="H62" s="20" t="s">
         <v>63</v>
@@ -9128,11 +9125,11 @@
       <c r="K62" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L62" s="7" t="s">
-        <v>310</v>
+      <c r="L62" s="15">
+        <v>5.0</v>
       </c>
       <c r="M62" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N62" s="7" t="s">
         <v>52</v>
@@ -9223,16 +9220,16 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="21"/>
       <c r="D63" s="22"/>
       <c r="E63" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="F63" s="12" t="s">
         <v>329</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>330</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>179</v>
@@ -9249,11 +9246,11 @@
       <c r="K63" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L63" s="7" t="s">
-        <v>310</v>
+      <c r="L63" s="15">
+        <v>5.0</v>
       </c>
       <c r="M63" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N63" s="7" t="s">
         <v>52</v>
@@ -9344,19 +9341,19 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="21"/>
       <c r="D64" s="22"/>
       <c r="E64" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="G64" s="13" t="s">
         <v>334</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>335</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>48</v>
@@ -9370,8 +9367,8 @@
       <c r="K64" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L64" s="7" t="s">
-        <v>310</v>
+      <c r="L64" s="15">
+        <v>5.0</v>
       </c>
       <c r="M64" s="12" t="s">
         <v>185</v>
@@ -9465,16 +9462,16 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="22"/>
       <c r="E65" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="F65" s="12" t="s">
         <v>337</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>338</v>
       </c>
       <c r="G65" s="9">
         <v>41674.0</v>
@@ -9491,11 +9488,11 @@
       <c r="K65" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L65" s="7" t="s">
-        <v>310</v>
+      <c r="L65" s="15">
+        <v>5.0</v>
       </c>
       <c r="M65" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N65" s="7" t="s">
         <v>52</v>
